--- a/content/B2-محتوا.xlsx
+++ b/content/B2-محتوا.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>موضوع محتوایی</t>
+          <t>ماموریت درس</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>مفاهیم انتزاعی</t>
+          <t>درباره ایده‌های پیچیده دقیق حرف بزن</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>داده و روند</t>
+          <t>داده‌ها و روندها را توضیح بده</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>تحلیل علت</t>
+          <t>چرایی اتفاق‌ها را تحلیل کن</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>افسوس گذشته</t>
+          <t>از «ای کاش»های گذشته بگو</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>بازخوانی تصمیم</t>
+          <t>تصمیم‌های گذشته را دوباره بسنج</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>پیامد امروزِ گذشته</t>
+          <t>اثر گذشته روی امروز را توضیح بده</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>فرض‌های جایگزین</t>
+          <t>سناریوهای جایگزین بساز</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ترجیح و توصیه قاطع</t>
+          <t>قاطعانه ترجیح و توصیه کن</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>پذیرش و رها کردن</t>
+          <t>پذیرش و رها کردن را طبیعی بگو</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>توضیح دشواری</t>
+          <t>دشواری و هدف را دقیق توضیح بده</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>فشرده‌سازی جمله</t>
+          <t>جمله‌ها را کوتاه‌تر و حرفه‌ای‌تر کن</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>تأکید و شگفتی</t>
+          <t>روی حرفت تأکید حرفه‌ای بگذار</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>تأکید بر یک بخش</t>
+          <t>روی بخش مهم جمله زوم کن</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ارزش‌ها و اولویت</t>
+          <t>از ارزش‌ها و اولویت‌ها بگو</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>بیان قاطع</t>
+          <t>نظرت را محکم و روشن بیان کن</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>احتیاط در ادعا</t>
+          <t>بدون ادعای مطلق حرف بزن</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>عدد و اندازه</t>
+          <t>عدد و اندازه را تقریبی بگو</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>استدلال شرطی</t>
+          <t>از یک فرض، نتیجه منطقی بگیر</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>موافقت جزئی</t>
+          <t>تا حدی موافق باش، نه صفر و صد</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ارائه و سخنرانی</t>
+          <t>یک ارائه حرفه‌ای شروع کن</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>مکاتبه کاری</t>
+          <t>مکاتبه کاری حرفه‌ای بنویس</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>گزارش‌نویسی</t>
+          <t>داده را به گزارش تبدیل کن</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>تنظیم لحن</t>
+          <t>لحن درست را برای هر موقعیت انتخاب کن</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>زبان روزمره اصطلاحی</t>
+          <t>مثل انگلیسی‌زبان‌ها اصطلاح به‌کار ببر</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ترکیب‌های ثابت</t>
+          <t>ترکیب‌های درست و طبیعی بساز</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>فعل‌های چندمعنایی</t>
+          <t>get / take / put را طبیعی استفاده کن</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>طبیعی حرف زدن</t>
+          <t>طبیعی‌تر و روان‌تر حرف بزن</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>متقاعد کردن</t>
+          <t>یک استدلال قانع‌کننده بساز</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>دفاع از موضع</t>
+          <t>اعتراض را پیش‌بینی و جواب بده</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>جمع‌بندی سطح</t>
+          <t>B2 تمام؛ درِ C1 باز شد</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">

--- a/content/B2-محتوا.xlsx
+++ b/content/B2-محتوا.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ماموریت درس</t>
+          <t>موضوع محتوایی</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>درباره ایده‌های پیچیده دقیق حرف بزن</t>
+          <t>مفاهیم انتزاعی</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>داده‌ها و روندها را توضیح بده</t>
+          <t>داده و روند</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>چرایی اتفاق‌ها را تحلیل کن</t>
+          <t>تحلیل علت</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>از «ای کاش»های گذشته بگو</t>
+          <t>افسوس گذشته</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>تصمیم‌های گذشته را دوباره بسنج</t>
+          <t>بازخوانی تصمیم</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>اثر گذشته روی امروز را توضیح بده</t>
+          <t>پیامد امروزِ گذشته</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>سناریوهای جایگزین بساز</t>
+          <t>فرض‌های جایگزین</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>قاطعانه ترجیح و توصیه کن</t>
+          <t>ترجیح و توصیه قاطع</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>پذیرش و رها کردن را طبیعی بگو</t>
+          <t>پذیرش و رها کردن</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>دشواری و هدف را دقیق توضیح بده</t>
+          <t>توضیح دشواری</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>جمله‌ها را کوتاه‌تر و حرفه‌ای‌تر کن</t>
+          <t>فشرده‌سازی جمله</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>روی حرفت تأکید حرفه‌ای بگذار</t>
+          <t>تأکید و شگفتی</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>روی بخش مهم جمله زوم کن</t>
+          <t>تأکید بر یک بخش</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>از ارزش‌ها و اولویت‌ها بگو</t>
+          <t>ارزش‌ها و اولویت</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>نظرت را محکم و روشن بیان کن</t>
+          <t>بیان قاطع</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>بدون ادعای مطلق حرف بزن</t>
+          <t>احتیاط در ادعا</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>عدد و اندازه را تقریبی بگو</t>
+          <t>عدد و اندازه</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>از یک فرض، نتیجه منطقی بگیر</t>
+          <t>استدلال شرطی</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>تا حدی موافق باش، نه صفر و صد</t>
+          <t>موافقت جزئی</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>یک ارائه حرفه‌ای شروع کن</t>
+          <t>ارائه و سخنرانی</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>مکاتبه کاری حرفه‌ای بنویس</t>
+          <t>مکاتبه کاری</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>داده را به گزارش تبدیل کن</t>
+          <t>گزارش‌نویسی</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>لحن درست را برای هر موقعیت انتخاب کن</t>
+          <t>تنظیم لحن</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>مثل انگلیسی‌زبان‌ها اصطلاح به‌کار ببر</t>
+          <t>زبان روزمره اصطلاحی</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ترکیب‌های درست و طبیعی بساز</t>
+          <t>ترکیب‌های ثابت</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>get / take / put را طبیعی استفاده کن</t>
+          <t>فعل‌های چندمعنایی</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>طبیعی‌تر و روان‌تر حرف بزن</t>
+          <t>طبیعی حرف زدن</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>یک استدلال قانع‌کننده بساز</t>
+          <t>متقاعد کردن</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>اعتراض را پیش‌بینی و جواب بده</t>
+          <t>دفاع از موضع</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>B2 تمام؛ درِ C1 باز شد</t>
+          <t>جمع‌بندی سطح</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">

--- a/content/B2-محتوا.xlsx
+++ b/content/B2-محتوا.xlsx
@@ -47552,7 +47552,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -47936,7 +47936,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -48320,7 +48320,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -48708,7 +48708,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -49092,7 +49092,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -49860,7 +49860,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -50244,7 +50244,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -50628,7 +50628,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -51012,7 +51012,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -51396,7 +51396,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -51780,7 +51780,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -52164,7 +52164,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -52552,7 +52552,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -52936,7 +52936,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -53320,7 +53320,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -53704,7 +53704,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -54088,7 +54088,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -54472,7 +54472,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -55244,7 +55244,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -55628,7 +55628,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -56016,7 +56016,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -56400,7 +56400,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -56784,7 +56784,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -57168,7 +57168,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -57552,7 +57552,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -57936,7 +57936,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -58320,7 +58320,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -58704,7 +58704,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
